--- a/Config/Datas/Tables/j_技能战斗_SkillCombatConfig.xlsx
+++ b/Config/Datas/Tables/j_技能战斗_SkillCombatConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkillCombat" sheetId="1" r:id="Rfe18fc3c0fc4441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkillCombat" sheetId="1" r:id="R37381aab58dd4c7b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1210,10 +1210,10 @@
         <x:v>baseIntervalMilli</x:v>
       </x:c>
       <x:c r="E1" s="24" t="str">
-        <x:v>rangeMilli</x:v>
+        <x:v>rangePixels</x:v>
       </x:c>
       <x:c r="F1" s="24" t="str">
-        <x:v>projectileSpeedMilli</x:v>
+        <x:v>projectileSpeedPixelsPerSecond</x:v>
       </x:c>
       <x:c r="G1" s="24" t="str">
         <x:v>projectileLifetimeMilli</x:v>
@@ -1236,10 +1236,10 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="E2" s="26" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="F2" s="26" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="G2" s="26" t="str">
         <x:v>int?</x:v>
@@ -1274,10 +1274,10 @@
         <x:v>基础攻击间隔，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
       </x:c>
       <x:c r="E4" s="30" t="str">
-        <x:v>攻击范围，按碰撞体边缘，世界单位；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
+        <x:v>攻击范围；按碰撞体边缘，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="F4" s="30" t="str">
-        <x:v>弹丸速度，世界单位每秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
+        <x:v>弹丸速度，逻辑像素/秒；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="G4" s="30" t="str">
         <x:v>弹丸寿命，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
@@ -1298,10 +1298,10 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="E5" s="36" t="n">
-        <x:v>6000</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="F5" s="36" t="n">
-        <x:v>12000</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="G5" s="36" t="n">
         <x:v>10000</x:v>
@@ -1320,7 +1320,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="E6" s="36" t="n">
-        <x:v>410</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F6" s="36"/>
       <x:c r="G6" s="36"/>
@@ -1340,7 +1340,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="E7" s="36" t="n">
-        <x:v>6000</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="F7" s="36"/>
       <x:c r="G7" s="36"/>
